--- a/output/2026-08-31_20_Italia_Emilia_Romagna_ATEX_Equipment_Services.xlsx
+++ b/output/2026-08-31_20_Italia_Emilia_Romagna_ATEX_Equipment_Services.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ATEX confermato (impianto aspirazione ATEX polveri ottone documentato)</t>
+          <t>ATEX confermato (impianto aspirazione ATEX polveri ottone documentato) [DUPLICATO — vedi anche: 2026-08-31_17_Italia_Emilia_Romagna_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ATEX confermato (pagina prodotto dedicata impianti ATEX)</t>
+          <t>ATEX confermato (pagina prodotto dedicata impianti ATEX) [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ATEX confermato (aspiratori certificati ATEX a catalogo)</t>
+          <t>ATEX confermato (aspiratori certificati ATEX a catalogo) [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ATEX confermato (aspiratori industriali ATEX per polveri combustibili)</t>
+          <t>ATEX confermato (aspiratori industriali ATEX per polveri combustibili) [DUPLICATO — vedi anche: 2026-08-31_13_Italia_Toscana_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stessa ragione sociale della riga precedente, sede separata; non e' duplicato</t>
+          <t>Stessa ragione sociale della riga precedente, sede separata; non e' duplicato [DUPLICATO — vedi anche: 2026-08-31_13_Italia_Toscana_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -746,10 +746,9 @@
           <t>0463 600361</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sede legale extraregionale (Trentino) ma progetto ATEX documentato in provincia di Modena/Reggio Emilia/Bologna: valutare se in target</t>
+          <t>Sede legale extraregionale (Trentino) ma progetto ATEX documentato in provincia di Modena/Reggio Emilia/Bologna: valutare se in target [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -833,7 +832,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ATEX plausibile (aspiratori per polveri esplosive), non confermato al 100%</t>
+          <t>ATEX plausibile (aspiratori per polveri esplosive), non confermato al 100% [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -910,7 +909,6 @@
           <t>059 361164</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Distributore componentistica generica (oleodinamica/pneumatica/elettromeccanica); nessuna evidenza pubblica di gamma ATEX dedicata, da qualificare telefonicamente</t>
@@ -943,8 +941,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Consulenza rischio ATEX/prevenzione incendi; ATEX plausibile, servizio non equipment</t>
@@ -989,7 +985,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fit ATEX specifico non confermato da fonti pubbliche; 0541 827127 riportato altrove come fax, non secondo telefono - verificare</t>
+          <t>Fit ATEX specifico non confermato da fonti pubbliche; 0541 827127 riportato altrove come fax, non secondo telefono - verificare [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1031,7 +1027,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Impianti aeraulici/aspirazione generici; ATEX non confermato da fonti pubbliche</t>
+          <t>Impianti aeraulici/aspirazione generici; ATEX non confermato da fonti pubbliche [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1066,7 +1062,6 @@
           <t>329 2520901</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Assistenza Aertecnica (aspirazione centralizzata); fit ATEX non confermato, settore adiacente</t>
@@ -1104,7 +1099,6 @@
           <t>0544 255996 / 349 2444024</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Settore adiacente (pulizia industriale generica), ATEX non confermato</t>
@@ -1149,7 +1143,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Settore adiacente (pulizia industriale generica), ATEX non confermato</t>
+          <t>Settore adiacente (pulizia industriale generica), ATEX non confermato [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1164,7 +1158,6 @@
           <t>Ice Italia S.r.l.</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>PC - Piacenza</t>
@@ -1180,7 +1173,6 @@
           <t>0523 346832</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Settore adiacente (attrezzature pulizia industriale), nessun sito proprio trovato, ATEX non confermato</t>
